--- a/results/final_20260514_v2_summary/VirusPseAAC_PartialAbstention_summary.xlsx
+++ b/results/final_20260514_v2_summary/VirusPseAAC_PartialAbstention_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:BU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,100 +476,320 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>afrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>arec__0.0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>arec__0.1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>arec__0.2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>arec__0.3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.0</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>rec__0.0</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>rec__0.1</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>rec__0.2</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>rec__0.3</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.0</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.1</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.3</t>
         </is>
@@ -623,100 +843,320 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>0.5755±0.1061</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.5936±0.1170</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.5553±0.1081</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.4778±0.1070</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.8582±0.0230</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.8730±0.0221</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.8818±0.0348</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0.8791±0.0323</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.5108±0.0871</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.5251±0.0679</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.4862±0.0818</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.4287±0.0901</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.5565±0.0911</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.5974±0.0694</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.5724±0.0749</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.5221±0.0919</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0.5147±0.0858</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>0.5420±0.0634</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>0.5093±0.0763</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.4548±0.0869</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>0.7841±0.0355</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>0.7731±0.0335</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.7359±0.0520</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.6821±0.0438</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.4769±0.0823</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.5027±0.0618</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.4703±0.0803</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.4170±0.0882</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.2991±0.0776</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.3571±0.0875</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.3412±0.0727</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.3334±0.0799</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.2629±0.0762</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.3297±0.1027</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.3070±0.0887</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.2807±0.0762</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.3652±0.0836</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.4306±0.0926</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.4339±0.0782</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.4843±0.1317</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.9947±0.0261</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.9684±0.0451</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.8892±0.1130</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.5674±0.0658</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.6001±0.0583</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.5806±0.0724</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.5257±0.0712</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.4950±0.0721</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.5130±0.0634</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.4767±0.0726</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.4057±0.0709</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.6706±0.0751</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.7284±0.0692</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.7497±0.0866</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.7572±0.0805</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>0.4157±0.0747</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>0.4668±0.0746</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.4978±0.1376</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>0.5033±0.1172</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>0.3634±0.0752</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.3860±0.0700</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.3561±0.1020</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.3082±0.1062</t>
         </is>
@@ -770,100 +1210,320 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>0.5902±0.1001</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.6027±0.1149</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.5572±0.1095</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.4795±0.1115</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>0.8566±0.0258</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.8710±0.0221</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.8805±0.0356</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0.8787±0.0316</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.5055±0.0865</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.5195±0.0664</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.4835±0.0812</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.4291±0.0878</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.5700±0.0899</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.6011±0.0705</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.5742±0.0738</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.5313±0.0878</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0.5166±0.0847</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0.5397±0.0635</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>0.5081±0.0753</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.4578±0.0839</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>0.7822±0.0388</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>0.7696±0.0336</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.7337±0.0513</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.6819±0.0411</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.4743±0.0835</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.4976±0.0612</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.4681±0.0794</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.4179±0.0864</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.3007±0.0773</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.3561±0.0883</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.3402±0.0726</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.3404±0.0762</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.2629±0.0745</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.3275±0.1037</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.3035±0.0877</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.2891±0.0756</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.3721±0.0886</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.4326±0.0935</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.4353±0.0793</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.4966±0.1237</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.9947±0.0261</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.9671±0.0457</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.8789±0.1142</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.5718±0.0685</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.5979±0.0590</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.5793±0.0714</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.5292±0.0648</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.4935±0.0710</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.5072±0.0624</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.4738±0.0722</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.4064±0.0668</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.6858±0.0874</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.7329±0.0673</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.7522±0.0836</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.7694±0.0692</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
         <is>
           <t>0.4010±0.0833</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>0.4551±0.0736</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.4939±0.1370</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>0.5005±0.1192</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>0.3476±0.0834</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.3726±0.0683</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.3512±0.1004</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.3043±0.1088</t>
         </is>
@@ -917,100 +1577,320 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>0.5704±0.1002</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.5923±0.1162</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.5558±0.1070</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.4790±0.1085</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0.8582±0.0240</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0.8728±0.0222</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0.8809±0.0349</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0.8792±0.0315</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.5134±0.0835</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.5245±0.0682</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.4825±0.0833</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.4289±0.0906</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.5565±0.0933</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.5962±0.0707</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.5677±0.0773</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.5209±0.0928</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0.5165±0.0841</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>0.5412±0.0641</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>0.5052±0.0782</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>0.4547±0.0873</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>0.7841±0.0362</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>0.7729±0.0336</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>0.7336±0.0513</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>0.6819±0.0429</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.4795±0.0791</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.5022±0.0622</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.4666±0.0821</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.4173±0.0886</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0.2995±0.0747</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.3569±0.0876</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0.3387±0.0715</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0.3313±0.0813</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.2640±0.0732</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.3296±0.1027</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.3051±0.0883</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.2791±0.0779</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.3634±0.0814</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.4300±0.0928</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.4307±0.0763</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.4819±0.1311</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.9947±0.0261</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.9684±0.0451</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.8949±0.1066</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.5675±0.0684</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>0.5993±0.0594</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.5768±0.0732</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.5252±0.0715</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.4967±0.0707</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.5125±0.0639</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.4738±0.0732</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>0.4059±0.0712</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0.6674±0.0842</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>0.7271±0.0713</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.7440±0.0877</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.7546±0.0828</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
         <is>
           <t>0.4204±0.0683</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>0.4668±0.0746</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>0.4958±0.1375</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>0.5043±0.1158</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>0.3685±0.0683</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>0.3860±0.0700</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>0.3535±0.1025</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>0.3092±0.1063</t>
         </is>
@@ -1064,100 +1944,320 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>0.5902±0.1001</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.6018±0.1138</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.5568±0.1095</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.4792±0.1116</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>0.8566±0.0258</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0.8709±0.0226</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.8799±0.0355</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0.8789±0.0312</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.5055±0.0865</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.5190±0.0673</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.4809±0.0829</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.4303±0.0878</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.5700±0.0899</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.6011±0.0705</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.5716±0.0759</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.5325±0.0886</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0.5166±0.0847</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>0.5393±0.0640</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>0.5055±0.0772</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>0.4590±0.0842</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>0.7822±0.0388</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>0.7693±0.0339</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>0.7320±0.0511</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>0.6821±0.0410</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.4743±0.0835</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.4971±0.0622</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.4655±0.0810</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.4191±0.0863</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>0.3007±0.0773</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>0.3562±0.0883</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>0.3393±0.0722</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0.3398±0.0766</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0.2629±0.0745</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.3276±0.1037</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.3029±0.0876</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.2885±0.0762</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.3721±0.0886</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.4326±0.0935</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.4339±0.0788</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.4967±0.1237</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.9947±0.0261</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.9671±0.0457</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.8812±0.1136</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>0.5718±0.0685</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>0.5977±0.0594</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.5769±0.0718</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.5299±0.0649</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>0.4935±0.0710</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>0.5070±0.0629</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.4719±0.0729</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>0.4071±0.0669</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>0.6858±0.0874</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>0.7329±0.0673</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.7489±0.0828</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.7698±0.0692</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
         <is>
           <t>0.4010±0.0833</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>0.4542±0.0765</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>0.4920±0.1370</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>0.5014±0.1178</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>0.3476±0.0834</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>0.3716±0.0710</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>0.3486±0.1014</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>0.3054±0.1076</t>
         </is>
@@ -1211,100 +2311,320 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>0.5031±0.0983</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.5197±0.0828</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.5416±0.1008</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.4361±0.1007</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>0.8486±0.0225</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0.8377±0.0283</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>0.8135±0.0344</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0.7615±0.0326</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.5325±0.1018</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.5221±0.0690</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0.4844±0.0775</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0.4120±0.0483</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.5366±0.0883</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.5640±0.0583</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.5733±0.0643</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.5625±0.0649</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0.5190±0.0909</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>0.5212±0.0604</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>0.5003±0.0681</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>0.4528±0.0486</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>0.7854±0.0393</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>0.7697±0.0379</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>0.7500±0.0299</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>0.6954±0.0433</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.4874±0.0846</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.4770±0.0630</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.4433±0.0681</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.3856±0.0426</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>0.3172±0.1060</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>0.3572±0.0871</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>0.3461±0.0825</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0.3364±0.0724</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0.3211±0.1392</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.3715±0.1018</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.3338±0.0917</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.3003±0.0695</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.3496±0.1024</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.3984±0.1008</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0.4134±0.0933</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.4538±0.1068</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.9965±0.0122</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.9668±0.0612</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.8526±0.1602</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>0.5519±0.0844</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>0.5538±0.0566</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.5326±0.0647</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.4717±0.0556</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>0.5207±0.0904</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>0.5061±0.0623</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>0.4659±0.0694</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>0.3811±0.0511</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>0.5882±0.0785</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>0.6141±0.0587</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.6267±0.0722</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.6232±0.0742</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
         <is>
           <t>0.4348±0.0480</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>0.3854±0.0930</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>0.3074±0.0941</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>0.2106±0.0504</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>0.3916±0.0713</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>0.3451±0.0835</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>0.2757±0.0715</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>0.1974±0.0506</t>
         </is>
@@ -1358,100 +2678,320 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>0.5416±0.0889</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.5541±0.0751</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.5693±0.1054</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.4263±0.0769</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>0.8406±0.0227</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.8309±0.0256</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.8051±0.0368</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0.7383±0.0367</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0.5130±0.0853</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.5052±0.0547</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0.4700±0.0748</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0.3897±0.0475</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.5713±0.0931</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.6038±0.0494</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.6143±0.0599</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.6202±0.0751</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0.5176±0.0832</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>0.5264±0.0484</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>0.5081±0.0635</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>0.4554±0.0500</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>0.7777±0.0358</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>0.7629±0.0312</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>0.7400±0.0339</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>0.6685±0.0443</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.4681±0.0752</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.4695±0.0529</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.4420±0.0662</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.3713±0.0435</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>0.3200±0.1040</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>0.3597±0.0756</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>0.3523±0.0834</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0.3371±0.0546</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.3167±0.1354</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.3636±0.0892</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.3300±0.0866</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.2779±0.0558</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.3670±0.1041</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.4179±0.0855</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.4400±0.1031</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.5136±0.0941</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.9950±0.0170</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.9633±0.0626</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.8518±0.1465</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>0.5591±0.0735</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>0.5638±0.0517</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.5436±0.0633</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.4745±0.0528</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.5051±0.0705</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.4936±0.0549</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0.4564±0.0683</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>0.3633±0.0466</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>0.6276±0.0831</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>0.6608±0.0612</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>0.6781±0.0660</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.6878±0.0714</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
         <is>
           <t>0.3623±0.0396</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>0.3410±0.0874</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>0.2777±0.1018</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>0.1557±0.0569</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>0.3183±0.0553</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>0.2995±0.0774</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>0.2487±0.0809</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>0.1432±0.0570</t>
         </is>
@@ -1505,100 +3045,320 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>0.4951±0.0976</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.5096±0.0835</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.5328±0.0958</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.4370±0.1004</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>0.8478±0.0225</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.8385±0.0280</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.8160±0.0317</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>0.7644±0.0331</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0.5373±0.1003</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.5224±0.0744</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0.4886±0.0720</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0.4173±0.0499</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.5288±0.0818</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.5479±0.0656</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.5616±0.0658</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.5541±0.0632</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0.5178±0.0883</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>0.5159±0.0670</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>0.4986±0.0649</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>0.4537±0.0499</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>0.7842±0.0394</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>0.7707±0.0402</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>0.7521±0.0291</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>0.6984±0.0428</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.4869±0.0848</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.4770±0.0687</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0.4455±0.0637</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.3907±0.0449</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>0.3146±0.1066</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>0.3563±0.0885</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>0.3446±0.0810</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>0.3359±0.0762</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0.3206±0.1391</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.3725±0.1038</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.3343±0.0920</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.3003±0.0700</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.3437±0.1047</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.3913±0.0971</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.4067±0.0892</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.4467±0.1070</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.9965±0.0122</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.9669±0.0666</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.8538±0.1549</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.5447±0.0833</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>0.5500±0.0628</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.5300±0.0619</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.4713±0.0562</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.5193±0.0902</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.5100±0.0692</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>0.4686±0.0659</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>0.3834±0.0518</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>0.5738±0.0775</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>0.5993±0.0617</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>0.6149±0.0710</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.6157±0.0760</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
         <is>
           <t>0.4396±0.0591</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>0.3991±0.0902</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>0.3218±0.0847</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>0.2270±0.0540</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>0.3929±0.0851</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>0.3606±0.0838</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>0.2892±0.0658</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>0.2141±0.0538</t>
         </is>
@@ -1652,100 +3412,320 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>0.5501±0.0953</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.5503±0.0716</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.5687±0.1058</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.4285±0.0827</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>0.8422±0.0212</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.8311±0.0261</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.8059±0.0374</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0.7385±0.0364</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0.5213±0.0766</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.5045±0.0568</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0.4754±0.0734</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0.3900±0.0480</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.5842±0.0821</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.6043±0.0536</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.6231±0.0536</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.6243±0.0720</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0.5274±0.0736</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>0.5268±0.0515</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>0.5147±0.0605</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>0.4570±0.0494</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>0.7801±0.0335</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>0.7618±0.0330</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>0.7412±0.0319</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>0.6684±0.0434</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.4765±0.0668</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.4707±0.0548</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0.4477±0.0644</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.3716±0.0448</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>0.3235±0.1019</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>0.3643±0.0791</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>0.3562±0.0815</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0.3401±0.0568</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.3200±0.1353</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.3647±0.0925</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.3370±0.0936</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.2837±0.0598</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.3719±0.1016</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.4205±0.0886</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.4450±0.1005</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.5094±0.0915</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.9950±0.0170</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.9577±0.0643</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.8446±0.1607</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>0.5682±0.0643</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>0.5644±0.0525</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.5483±0.0617</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.4769±0.0504</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>0.5119±0.0637</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.4941±0.0558</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.4597±0.0682</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>0.3661±0.0457</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>0.6402±0.0715</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>0.6613±0.0593</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.6856±0.0632</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.6881±0.0658</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
         <is>
           <t>0.3623±0.0396</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>0.3430±0.0879</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>0.2796±0.1033</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>0.1518±0.0574</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>0.3223±0.0502</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>0.3024±0.0770</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>0.2510±0.0815</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>0.1392±0.0579</t>
         </is>
